--- a/data/trans_orig/P77_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P77_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según cual es la persona sustentadora principal del hogar en 2023</t>
+          <t>Población según cual es la persona sustentadora principal del hogar en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66236</t>
+          <t>65984</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122160</t>
+          <t>122804</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>226789</t>
+          <t>230103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>326660</t>
+          <t>324355</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>341284</t>
+          <t>335099</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>426373</t>
+          <t>420286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>8641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>219387</t>
+          <t>195521</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>218075</t>
+          <t>229362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>511204</t>
+          <t>511290</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>567419</t>
+          <t>567851</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>288968</t>
+          <t>302632</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>411654</t>
+          <t>412623</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>797338</t>
+          <t>810964</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>969790</t>
+          <t>969506</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,25%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97193</t>
+          <t>81726</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224769</t>
+          <t>223432</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416427</t>
+          <t>416718</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>468019</t>
+          <t>468480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415508</t>
+          <t>408419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>697508</t>
+          <t>702216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,64%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>774</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>14851</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15055</t>
+          <t>17328</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23189</t>
+          <t>23121</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>963717</t>
+          <t>963455</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1093160</t>
+          <t>1109043</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>482863</t>
+          <t>482234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>535849</t>
+          <t>534634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1439199</t>
+          <t>1436613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1729232</t>
+          <t>1735560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102208</t>
+          <t>101261</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>163272</t>
+          <t>164222</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>377711</t>
+          <t>376222</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>704977</t>
+          <t>715911</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>485126</t>
+          <t>483301</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>970423</t>
+          <t>965566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>58,95%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,62 +1790,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2487</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>12791</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2487</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>13702</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>539835</t>
+          <t>539171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>600179</t>
+          <t>602405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>228389</t>
+          <t>217455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>555655</t>
+          <t>557144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>667207</t>
+          <t>671608</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1149802</t>
+          <t>1151714</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>123109</t>
+          <t>122430</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192284</t>
+          <t>190451</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>350607</t>
+          <t>357125</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>481846</t>
+          <t>483776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>523583</t>
+          <t>522724</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>643775</t>
+          <t>638840</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>734335</t>
+          <t>736142</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>803291</t>
+          <t>804054</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>610010</t>
+          <t>608251</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>739440</t>
+          <t>733811</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1376034</t>
+          <t>1379961</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1496121</t>
+          <t>1495482</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>432517</t>
+          <t>415608</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>614949</t>
+          <t>615693</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1539669</t>
+          <t>1536398</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2086105</t>
+          <t>2073449</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1994149</t>
+          <t>1996506</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2727441</t>
+          <t>2648552</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13801</t>
+          <t>13132</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>261254</t>
+          <t>269368</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>22895</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>277996</t>
+          <t>272694</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2833918</t>
+          <t>2835359</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3021578</t>
+          <t>3035655</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1558856</t>
+          <t>1582595</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2104820</t>
+          <t>2110337</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4397831</t>
+          <t>4481377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5094285</t>
+          <t>5103954</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
